--- a/artfynd/A 15258-2026 artfynd.xlsx
+++ b/artfynd/A 15258-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121430355</v>
+        <v>416332</v>
       </c>
       <c r="B2" t="n">
-        <v>108736</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101947</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220204</v>
+        <v>1449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Hällebräcka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Saxifraga osloënsis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Knaben</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Myrby, Upl</t>
+          <t>Myrby, 400 m N om, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>686357</v>
+        <v>686407</v>
       </c>
       <c r="R2" t="n">
-        <v>6671591</v>
+        <v>6671308</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,14 +738,24 @@
           <t>Harg</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>C-ÖST-0517</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>1991-06-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>1991-06-26</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ETI: UPPLAND: Östhammars kommun, Hargs s:n. 400 m N om Myrby. 6671319, 1641737, 100m / RUBIN 12I4iSV. 1991-06-26. Leg. Rickard Brock KOM: Det. Anna-Lena Anderberg (enligt etiketten). - Ej originaletikett</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,19 +766,842 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>1475</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Floraväkterisamordn C-län</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Rickard Brock</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>121430250</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Myrby, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>686383</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6671590</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Harg</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Anna-Lotta Hellqvist</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Anna-Lotta Hellqvist, Emma Hellkvist</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121430252</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Myrby, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>686346</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6671623</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Harg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anna-Lotta Hellqvist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anna-Lotta Hellqvist, Emma Hellkvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121430253</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Myrby, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>686395</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6671562</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Harg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anna-Lotta Hellqvist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anna-Lotta Hellqvist, Emma Hellkvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121430581</v>
+      </c>
+      <c r="B6" t="n">
+        <v>108194</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220103</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Klasefibbla</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Crepis praemorsa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Walther</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Myrby, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>686338</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6671643</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Harg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anna-Lotta Hellqvist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anna-Lotta Hellqvist, Emma Hellkvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>72871592</v>
+      </c>
+      <c r="B7" t="n">
+        <v>109815</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Myrby, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>686380</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6671587</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Harg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2018-07-19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2018-07-19</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121430354</v>
+      </c>
+      <c r="B8" t="n">
+        <v>109815</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Myrby, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>686383</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6671584</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Harg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anna-Lotta Hellqvist</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anna-Lotta Hellqvist, Emma Hellkvist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121430355</v>
+      </c>
+      <c r="B9" t="n">
+        <v>109815</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Myrby, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>686357</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6671591</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Harg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anna-Lotta Hellqvist</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anna-Lotta Hellqvist, Emma Hellkvist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121430356</v>
+      </c>
+      <c r="B10" t="n">
+        <v>109815</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Myrby, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>686366</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6671601</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Harg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anna-Lotta Hellqvist</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anna-Lotta Hellqvist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
